--- a/Mynew/Test.xlsx
+++ b/Mynew/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGitHub\mylims\Mynew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2779DE6B-AB56-4E6C-856E-E10EC3224F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D39C71-ADE9-4BD0-ACD7-3AA176D1F009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <t>my database</t>
   </si>
   <si>
-    <t>test</t>
+    <t>Yassine</t>
   </si>
 </sst>
 </file>
